--- a/worked_examples/AIHE-CASE05_ai_quality_management_accreditation_and_corrective_action/workbook/xlsx/AIHE-CASE05_worked_example_and_template.xlsx
+++ b/worked_examples/AIHE-CASE05_ai_quality_management_accreditation_and_corrective_action/workbook/xlsx/AIHE-CASE05_worked_example_and_template.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R2f175ec202334f4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Inputs" sheetId="2" r:id="R36392f7b731a4856"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="3" r:id="Ra765a694b1cf4c7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Summary" sheetId="4" r:id="R7826478b72ba4b00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="Rcaca42e023f44aa5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Inputs" sheetId="2" r:id="R9610fc98f25a4016"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank Template" sheetId="3" r:id="R2ee7cb5fe6174ac2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Summary" sheetId="4" r:id="Ra7cc7ac8200d4bfd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -44,8 +44,14 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF303236"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -77,6 +83,16 @@
         <x:fgColor rgb="FFFFF3CD"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6B2230"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F0E7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="38">
     <x:border/>
@@ -397,7 +413,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="109">
+  <x:cellXfs count="128">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -406,7 +422,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -414,7 +430,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -431,22 +447,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -463,22 +479,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -523,22 +539,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -553,22 +569,22 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -623,20 +639,20 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -659,6 +675,59 @@
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -711,9 +780,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -822,25 +891,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="110" t="str">
         <x:v>AI Quality-Control, Accreditation, and Corrective Action</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
+      <x:c r="B1" s="110"/>
+      <x:c r="C1" s="110"/>
+      <x:c r="D1" s="110"/>
+      <x:c r="E1" s="110"/>
+      <x:c r="F1" s="110"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5"/>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5"/>
+      <x:c r="A2" s="110"/>
+      <x:c r="B2" s="110"/>
+      <x:c r="C2" s="110"/>
+      <x:c r="D2" s="110"/>
+      <x:c r="E2" s="110"/>
+      <x:c r="F2" s="110"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="21" t="str">
+      <x:c r="A4" s="112" t="str">
         <x:v>Example ID</x:v>
       </x:c>
       <x:c r="B4" s="42" t="str">
@@ -848,7 +917,7 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="22" t="str">
+      <x:c r="A5" s="114" t="str">
         <x:v>Chapter</x:v>
       </x:c>
       <x:c r="B5" s="43" t="str">
@@ -856,7 +925,7 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="22" t="str">
+      <x:c r="A6" s="114" t="str">
         <x:v>Decision question</x:v>
       </x:c>
       <x:c r="B6" s="43" t="str">
@@ -864,7 +933,7 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="22" t="str">
+      <x:c r="A7" s="114" t="str">
         <x:v>Status</x:v>
       </x:c>
       <x:c r="B7" s="43" t="str">
@@ -872,7 +941,7 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="22" t="str">
+      <x:c r="A8" s="114" t="str">
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B8" s="43" t="str">
@@ -880,7 +949,7 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="22" t="str">
+      <x:c r="A9" s="114" t="str">
         <x:v>Release date</x:v>
       </x:c>
       <x:c r="B9" s="43" t="str">
@@ -888,7 +957,7 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="22" t="str">
+      <x:c r="A10" s="114" t="str">
         <x:v>How to use</x:v>
       </x:c>
       <x:c r="B10" s="43" t="str">
@@ -896,7 +965,7 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="22" t="str">
+      <x:c r="A11" s="114" t="str">
         <x:v>Related resources</x:v>
       </x:c>
       <x:c r="B11" s="43" t="str">
@@ -904,7 +973,7 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="23" t="str">
+      <x:c r="A12" s="116" t="str">
         <x:v>Data protection</x:v>
       </x:c>
       <x:c r="B12" s="44" t="str">
@@ -934,42 +1003,42 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="110" t="str">
         <x:v>Worked synthetic inputs and calculations</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="G1" s="5"/>
-      <x:c r="H1" s="5"/>
-      <x:c r="I1" s="5"/>
-      <x:c r="J1" s="5"/>
+      <x:c r="B1" s="110"/>
+      <x:c r="C1" s="110"/>
+      <x:c r="D1" s="110"/>
+      <x:c r="E1" s="110"/>
+      <x:c r="F1" s="110"/>
+      <x:c r="G1" s="110"/>
+      <x:c r="H1" s="110"/>
+      <x:c r="I1" s="110"/>
+      <x:c r="J1" s="110"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="57" t="str">
+      <x:c r="A3" s="121" t="str">
         <x:v>Month</x:v>
       </x:c>
-      <x:c r="B3" s="58" t="str">
+      <x:c r="B3" s="122" t="str">
         <x:v>False-negative rate</x:v>
       </x:c>
-      <x:c r="C3" s="58" t="str">
+      <x:c r="C3" s="122" t="str">
         <x:v>Alerts/day</x:v>
       </x:c>
-      <x:c r="D3" s="58" t="str">
+      <x:c r="D3" s="122" t="str">
         <x:v>Downtime hours</x:v>
       </x:c>
-      <x:c r="E3" s="59" t="str">
+      <x:c r="E3" s="123" t="str">
         <x:v>Complaints</x:v>
       </x:c>
-      <x:c r="F3" s="91" t="str">
+      <x:c r="F3" s="124" t="str">
         <x:v>Signal</x:v>
       </x:c>
-      <x:c r="H3" s="57" t="str">
+      <x:c r="H3" s="121" t="str">
         <x:v>Control</x:v>
       </x:c>
-      <x:c r="I3" s="59" t="str">
+      <x:c r="I3" s="123" t="str">
         <x:v>Value</x:v>
       </x:c>
     </x:row>
@@ -1256,28 +1325,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="110" t="str">
         <x:v>Blank template - replace synthetic values with governed local evidence</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
+      <x:c r="B1" s="110"/>
+      <x:c r="C1" s="110"/>
+      <x:c r="D1" s="110"/>
+      <x:c r="E1" s="110"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="57" t="str">
+      <x:c r="A3" s="121" t="str">
         <x:v>Month</x:v>
       </x:c>
-      <x:c r="B3" s="58" t="str">
+      <x:c r="B3" s="122" t="str">
         <x:v>False-negative rate</x:v>
       </x:c>
-      <x:c r="C3" s="58" t="str">
+      <x:c r="C3" s="122" t="str">
         <x:v>Alerts/day</x:v>
       </x:c>
-      <x:c r="D3" s="58" t="str">
+      <x:c r="D3" s="122" t="str">
         <x:v>Downtime hours</x:v>
       </x:c>
-      <x:c r="E3" s="59" t="str">
+      <x:c r="E3" s="123" t="str">
         <x:v>Complaints</x:v>
       </x:c>
     </x:row>
@@ -1410,28 +1479,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="110" t="str">
         <x:v>AI Quality-Control, Accreditation, and Corrective Action</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
+      <x:c r="B1" s="110"/>
+      <x:c r="C1" s="110"/>
+      <x:c r="D1" s="110"/>
+      <x:c r="E1" s="110"/>
+      <x:c r="F1" s="110"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="5"/>
-      <x:c r="B2" s="5"/>
-      <x:c r="C2" s="5"/>
-      <x:c r="D2" s="5"/>
-      <x:c r="E2" s="5"/>
-      <x:c r="F2" s="5"/>
+      <x:c r="A2" s="110"/>
+      <x:c r="B2" s="110"/>
+      <x:c r="C2" s="110"/>
+      <x:c r="D2" s="110"/>
+      <x:c r="E2" s="110"/>
+      <x:c r="F2" s="110"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="57" t="str">
+      <x:c r="A4" s="121" t="str">
         <x:v>Reference metric</x:v>
       </x:c>
-      <x:c r="B4" s="59" t="str">
+      <x:c r="B4" s="123" t="str">
         <x:v>Synthetic result</x:v>
       </x:c>
     </x:row>
@@ -1452,66 +1521,66 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="97" t="str">
+      <x:c r="A8" s="125" t="str">
         <x:v>Worked interpretation</x:v>
       </x:c>
-      <x:c r="B8" s="97"/>
-      <x:c r="C8" s="97"/>
-      <x:c r="D8" s="97"/>
-      <x:c r="E8" s="97"/>
-      <x:c r="F8" s="97"/>
+      <x:c r="B8" s="125"/>
+      <x:c r="C8" s="125"/>
+      <x:c r="D8" s="125"/>
+      <x:c r="E8" s="125"/>
+      <x:c r="F8" s="125"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="102" t="str">
+      <x:c r="A9" s="126" t="str">
         <x:v>The month-eight change breaches the false-negative limit and coincides with higher alert volume, downtime, and complaints. Immediate containment should restrict the updated version while the team reconstructs data, model, interface, and workflow changes. Closure requires evidence that corrective action restored performance, affected records and users were addressed, and version and update controls were improved.</x:v>
       </x:c>
-      <x:c r="B9" s="102"/>
-      <x:c r="C9" s="102"/>
-      <x:c r="D9" s="102"/>
-      <x:c r="E9" s="102"/>
-      <x:c r="F9" s="102"/>
+      <x:c r="B9" s="126"/>
+      <x:c r="C9" s="126"/>
+      <x:c r="D9" s="126"/>
+      <x:c r="E9" s="126"/>
+      <x:c r="F9" s="126"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="102"/>
-      <x:c r="B10" s="102"/>
-      <x:c r="C10" s="102"/>
-      <x:c r="D10" s="102"/>
-      <x:c r="E10" s="102"/>
-      <x:c r="F10" s="102"/>
+      <x:c r="A10" s="126"/>
+      <x:c r="B10" s="126"/>
+      <x:c r="C10" s="126"/>
+      <x:c r="D10" s="126"/>
+      <x:c r="E10" s="126"/>
+      <x:c r="F10" s="126"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="102"/>
-      <x:c r="B11" s="102"/>
-      <x:c r="C11" s="102"/>
-      <x:c r="D11" s="102"/>
-      <x:c r="E11" s="102"/>
-      <x:c r="F11" s="102"/>
+      <x:c r="A11" s="126"/>
+      <x:c r="B11" s="126"/>
+      <x:c r="C11" s="126"/>
+      <x:c r="D11" s="126"/>
+      <x:c r="E11" s="126"/>
+      <x:c r="F11" s="126"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="102"/>
-      <x:c r="B12" s="102"/>
-      <x:c r="C12" s="102"/>
-      <x:c r="D12" s="102"/>
-      <x:c r="E12" s="102"/>
-      <x:c r="F12" s="102"/>
+      <x:c r="A12" s="126"/>
+      <x:c r="B12" s="126"/>
+      <x:c r="C12" s="126"/>
+      <x:c r="D12" s="126"/>
+      <x:c r="E12" s="126"/>
+      <x:c r="F12" s="126"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="102"/>
-      <x:c r="B13" s="102"/>
-      <x:c r="C13" s="102"/>
-      <x:c r="D13" s="102"/>
-      <x:c r="E13" s="102"/>
-      <x:c r="F13" s="102"/>
+      <x:c r="A13" s="126"/>
+      <x:c r="B13" s="126"/>
+      <x:c r="C13" s="126"/>
+      <x:c r="D13" s="126"/>
+      <x:c r="E13" s="126"/>
+      <x:c r="F13" s="126"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="108" t="str">
+      <x:c r="A15" s="127" t="str">
         <x:v>Interpret calculations with evidence quality, uncertainty, mandatory safeguards, implementation capacity, monitoring, and exit conditions.</x:v>
       </x:c>
-      <x:c r="B15" s="108"/>
-      <x:c r="C15" s="108"/>
-      <x:c r="D15" s="108"/>
-      <x:c r="E15" s="108"/>
-      <x:c r="F15" s="108"/>
+      <x:c r="B15" s="127"/>
+      <x:c r="C15" s="127"/>
+      <x:c r="D15" s="127"/>
+      <x:c r="E15" s="127"/>
+      <x:c r="F15" s="127"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
